--- a/AAII_Financials/Yearly/INEO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/INEO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>INEO</t>
   </si>
@@ -715,10 +715,10 @@
         <v>58400</v>
       </c>
       <c r="E8" s="3">
-        <v>58300</v>
+        <v>62700</v>
       </c>
       <c r="F8" s="3">
-        <v>59500</v>
+        <v>62700</v>
       </c>
       <c r="G8" s="3">
         <v>51400</v>
@@ -745,10 +745,10 @@
         <v>47200</v>
       </c>
       <c r="E9" s="3">
-        <v>47400</v>
+        <v>50400</v>
       </c>
       <c r="F9" s="3">
-        <v>48600</v>
+        <v>50700</v>
       </c>
       <c r="G9" s="3">
         <v>42200</v>
@@ -775,10 +775,10 @@
         <v>11200</v>
       </c>
       <c r="E10" s="3">
-        <v>10900</v>
+        <v>12300</v>
       </c>
       <c r="F10" s="3">
-        <v>10900</v>
+        <v>12000</v>
       </c>
       <c r="G10" s="3">
         <v>9300</v>
@@ -909,10 +909,10 @@
         <v>400</v>
       </c>
       <c r="E15" s="3">
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
         <v>200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
@@ -950,10 +950,10 @@
         <v>58500</v>
       </c>
       <c r="E17" s="3">
-        <v>57500</v>
+        <v>61500</v>
       </c>
       <c r="F17" s="3">
-        <v>57000</v>
+        <v>59800</v>
       </c>
       <c r="G17" s="3">
         <v>49800</v>
@@ -980,10 +980,10 @@
         <v>-100</v>
       </c>
       <c r="E18" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="F18" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="G18" s="3">
         <v>1600</v>
@@ -1054,10 +1054,10 @@
         <v>600</v>
       </c>
       <c r="E21" s="3">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="F21" s="3">
-        <v>3100</v>
+        <v>3500</v>
       </c>
       <c r="G21" s="3">
         <v>2600</v>
@@ -1084,10 +1084,10 @@
         <v>1300</v>
       </c>
       <c r="E22" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F22" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G22" s="3">
         <v>600</v>
@@ -1114,10 +1114,10 @@
         <v>-1100</v>
       </c>
       <c r="E23" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F23" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="G23" s="3">
         <v>1900</v>
@@ -1204,10 +1204,10 @@
         <v>-400</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F26" s="3">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="G26" s="3">
         <v>1500</v>
@@ -1234,10 +1234,10 @@
         <v>-400</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F27" s="3">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="G27" s="3">
         <v>1500</v>
@@ -1414,10 +1414,10 @@
         <v>-400</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F33" s="3">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="G33" s="3">
         <v>1500</v>
@@ -1474,10 +1474,10 @@
         <v>-400</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F35" s="3">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="G35" s="3">
         <v>1500</v>
@@ -1567,7 +1567,7 @@
         <v>1100</v>
       </c>
       <c r="E41" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="F41" s="3">
         <v>700</v>
@@ -1597,7 +1597,7 @@
         <v>3900</v>
       </c>
       <c r="E42" s="3">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="F42" s="3">
         <v>3000</v>
@@ -1627,7 +1627,7 @@
         <v>12600</v>
       </c>
       <c r="E43" s="3">
-        <v>13200</v>
+        <v>16000</v>
       </c>
       <c r="F43" s="3">
         <v>14600</v>
@@ -1657,7 +1657,7 @@
         <v>18600</v>
       </c>
       <c r="E44" s="3">
-        <v>18100</v>
+        <v>19400</v>
       </c>
       <c r="F44" s="3">
         <v>19000</v>
@@ -1717,7 +1717,7 @@
         <v>36500</v>
       </c>
       <c r="E46" s="3">
-        <v>36800</v>
+        <v>41300</v>
       </c>
       <c r="F46" s="3">
         <v>37600</v>
@@ -1777,7 +1777,7 @@
         <v>2800</v>
       </c>
       <c r="E48" s="3">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="F48" s="3">
         <v>1500</v>
@@ -1896,8 +1896,8 @@
       <c r="D52" s="3">
         <v>1300</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="E52" s="3">
+        <v>1300</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1957,7 +1957,7 @@
         <v>41400</v>
       </c>
       <c r="E54" s="3">
-        <v>39600</v>
+        <v>45800</v>
       </c>
       <c r="F54" s="3">
         <v>39100</v>
@@ -2015,7 +2015,7 @@
         <v>5300</v>
       </c>
       <c r="E57" s="3">
-        <v>4600</v>
+        <v>4900</v>
       </c>
       <c r="F57" s="3">
         <v>4600</v>
@@ -2045,7 +2045,7 @@
         <v>17900</v>
       </c>
       <c r="E58" s="3">
-        <v>18300</v>
+        <v>19600</v>
       </c>
       <c r="F58" s="3">
         <v>16200</v>
@@ -2075,7 +2075,7 @@
         <v>11200</v>
       </c>
       <c r="E59" s="3">
-        <v>5600</v>
+        <v>12500</v>
       </c>
       <c r="F59" s="3">
         <v>13600</v>
@@ -2105,7 +2105,7 @@
         <v>34400</v>
       </c>
       <c r="E60" s="3">
-        <v>28600</v>
+        <v>37000</v>
       </c>
       <c r="F60" s="3">
         <v>34500</v>
@@ -2135,7 +2135,7 @@
         <v>1900</v>
       </c>
       <c r="E61" s="3">
-        <v>2100</v>
+        <v>3700</v>
       </c>
       <c r="F61" s="3">
         <v>1500</v>
@@ -2285,7 +2285,7 @@
         <v>36400</v>
       </c>
       <c r="E66" s="3">
-        <v>30700</v>
+        <v>40900</v>
       </c>
       <c r="F66" s="3">
         <v>36000</v>
@@ -2449,7 +2449,7 @@
         <v>4500</v>
       </c>
       <c r="E72" s="3">
-        <v>1800</v>
+        <v>4900</v>
       </c>
       <c r="F72" s="3">
         <v>1800</v>
@@ -2569,7 +2569,7 @@
         <v>5000</v>
       </c>
       <c r="E76" s="3">
-        <v>8900</v>
+        <v>4900</v>
       </c>
       <c r="F76" s="3">
         <v>3100</v>
@@ -2664,10 +2664,10 @@
         <v>-400</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F81" s="3">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="G81" s="3">
         <v>1500</v>
@@ -2708,10 +2708,10 @@
         <v>800</v>
       </c>
       <c r="E83" s="3">
+        <v>700</v>
+      </c>
+      <c r="F83" s="3">
         <v>600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>500</v>
       </c>
       <c r="G83" s="3">
         <v>300</v>
@@ -2888,10 +2888,10 @@
         <v>4400</v>
       </c>
       <c r="E89" s="3">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="F89" s="3">
-        <v>1600</v>
+        <v>3700</v>
       </c>
       <c r="G89" s="3">
         <v>-2100</v>
@@ -2932,10 +2932,10 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="F91" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="G91" s="3">
         <v>-300</v>
@@ -3022,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="F94" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="G94" s="3">
         <v>-300</v>
@@ -3189,7 +3189,7 @@
         <v>-600</v>
       </c>
       <c r="F100" s="3">
-        <v>-1500</v>
+        <v>-3800</v>
       </c>
       <c r="G100" s="3">
         <v>2100</v>
@@ -3216,7 +3216,7 @@
         <v>300</v>
       </c>
       <c r="E101" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
@@ -3246,7 +3246,7 @@
         <v>-700</v>
       </c>
       <c r="E102" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F102" s="3">
         <v>-300</v>
